--- a/assets.xlsx.xlsx
+++ b/assets.xlsx.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W253"/>
+  <dimension ref="A1:W266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30012,6 +30012,1527 @@
         </is>
       </c>
       <c r="W253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>LUC-AIO-020</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>All-in-One</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>All-in-One</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>10160</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>CS02115041</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Intel (R) Celeron (R) CPU J1800 @ 2.41 GHz</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>4.00 GB</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>238 GB</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Windows 10 Education</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>5C-93-A2-A6-53-33</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Junior Teachers</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Junior College</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>For admission purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>LUC-PRN-008</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Printer</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Printer</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>HP LaserJet P1106</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>VNF5301330</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Junior Teachers</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Junior College</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-008</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>MW560N</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>PBS3S0176305Y</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Classroom 302</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Classroom 302</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-009</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>MW560N</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>PBJ1S01286000</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Classroom 303</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Classroom 303</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-010</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>MW560N</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>PBS3S0170305Y</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Classroom 304</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Classroom 304</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-011</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>MW560N</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>PBJ1S01079000</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Classroom 401</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Classroom 401</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-012</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>MW560N</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>PBY6S0109005Y</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Classroom 402</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Classroom 402</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-013</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>MW560N</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>PBJ1S01155000</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Classroom 403</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Classroom 403</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-014</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>EPSON</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>PD45J0030004E</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Classroom 404</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Classroom 404</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-015</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>MS531P</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>PD45J0005304E</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>IT Lab 501</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>IT Lab 501</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-016</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>MW560N</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>PBS3S0173905Y</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Classroom 502</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Classroom 502</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-017</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>MW560N</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>PBS3S0151205Y</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Classroom 503</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Classroom 503</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>LUC-PRJ-018</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>BENQ</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>MW560N</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>PBJ1S01176000</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>MAIN STORE</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Classroom 504</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Classroom 504</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
         <is>
           <t>-</t>
         </is>
